--- a/Test case/CAB Test Case.xlsx
+++ b/Test case/CAB Test Case.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4a55f3563615e35/Desktop/LTHDV/23646731_TranQuocKhang_Cabsystem/Test case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{3A8E3571-F2A7-456E-A457-F92F800A3BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0E9D68E-AF78-4087-8134-95343E502393}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="8_{3A8E3571-F2A7-456E-A457-F92F800A3BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{349E8DC3-4CE1-4077-B0ED-C1CB57CD39B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="996" firstSheet="4" activeTab="7" xr2:uid="{45BDFBF9-899E-4BC7-B867-79EAD29F6805}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="996" firstSheet="5" activeTab="7" xr2:uid="{45BDFBF9-899E-4BC7-B867-79EAD29F6805}"/>
   </bookViews>
   <sheets>
     <sheet name="Register Test Cases" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="841">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -131,27 +131,15 @@
     <t>Đăng nhập với username và password hợp lệ</t>
   </si>
   <si>
-    <t>1. Mở Login2. Nhập username3. Nhập password4. Nhấn Login</t>
-  </si>
-  <si>
-    <t>Username: user01Password: Password@123</t>
-  </si>
-  <si>
     <t>TC-AUTH-007</t>
   </si>
   <si>
     <t>Đăng nhập với username không tồn tại</t>
   </si>
   <si>
-    <t>Username: unknown01Password: Password@123</t>
-  </si>
-  <si>
     <t>TC-AUTH-008</t>
   </si>
   <si>
-    <t>Username: user01Password: Wrong@123</t>
-  </si>
-  <si>
     <t>TC-AUTH-009</t>
   </si>
   <si>
@@ -164,15 +152,9 @@
     <t>TC-AUTH-012</t>
   </si>
   <si>
-    <t>Username: nullPassword: Password@123</t>
-  </si>
-  <si>
     <t>TC-AUTH-013</t>
   </si>
   <si>
-    <t>Username: user01Password: null</t>
-  </si>
-  <si>
     <t>TC-AUTH-014</t>
   </si>
   <si>
@@ -182,9 +164,6 @@
     <t>TC-AUTH-015</t>
   </si>
   <si>
-    <t>Username: user01Password: password@123</t>
-  </si>
-  <si>
     <t>HTTP 409; không tạo tài khoản mới</t>
   </si>
   <si>
@@ -887,18 +866,12 @@
     <t>TC-VEHICLE-041</t>
   </si>
   <si>
-    <t>Username: customer01Password: Password123!Full Name: Nguyen Van APhone: 0901234567Email: customer01@example.com</t>
-  </si>
-  <si>
     <t>Đăng ký Customer với toàn bộ thông tin hợp lệ</t>
   </si>
   <si>
     <t>Hệ thống hoạt động; username/email/phone chưa tồn tại</t>
   </si>
   <si>
-    <t>1. Mở Register2. Nhập username3. Nhập password4. Nhập họ tên, phone, email5. Nhấn Register</t>
-  </si>
-  <si>
     <t>Đăng ký thành công; tạo tài khoản Customer; HTTP 201</t>
   </si>
   <si>
@@ -908,9 +881,6 @@
     <t>Hệ thống hoạt động</t>
   </si>
   <si>
-    <t>1. Mở Register2. Lần lượt bỏ từng trường bắt buộc3. Nhấn Register</t>
-  </si>
-  <si>
     <t>Thiếu lần lượt: username/password/fullName/phone/email</t>
   </si>
   <si>
@@ -920,18 +890,9 @@
     <t>Đăng ký với username, email hoặc phone đã tồn tại</t>
   </si>
   <si>
-    <t>1. Mở Register2. Nhập dữ liệu trùng3. Nhấn Register</t>
-  </si>
-  <si>
-    <t>Username: customer01Email: customer01@example.comPhone: 0901234567</t>
-  </si>
-  <si>
     <t>Đăng ký với email sai định dạng</t>
   </si>
   <si>
-    <t>1. Nhập thông tin đăng ký2. Nhập email sai format3. Nhấn Register</t>
-  </si>
-  <si>
     <t>HTTP 400; hiển thị lỗi email không hợp lệ</t>
   </si>
   <si>
@@ -941,18 +902,12 @@
     <t>API Register đang hoạt động</t>
   </si>
   <si>
-    <t>1. Mở chức năng Register2. Gửi body rỗng/null hoặc JSON sai cấu trúc</t>
-  </si>
-  <si>
     <t>HTTP 400; không tạo tài khoản; server không crash</t>
   </si>
   <si>
     <t>Rule độ dài các trường đã được định nghĩa</t>
   </si>
   <si>
-    <t>1. Nhập dữ liệu tại giới hạn dưới2. Đăng ký3. Nhập dữ liệu tại giới hạn trên4. Đăng ký</t>
-  </si>
-  <si>
     <t>Username/password/fullName/phone/email tại min/max length</t>
   </si>
   <si>
@@ -962,9 +917,6 @@
     <t>API hoạt động; có thể mô phỏng lỗi service/database</t>
   </si>
   <si>
-    <t>1. Nhập dữ liệu hợp lệ2. Nhấn Register3. Mô phỏng lỗi service/database</t>
-  </si>
-  <si>
     <t>Service/Database: unavailable</t>
   </si>
   <si>
@@ -986,9 +938,6 @@
     <t>Username tồn tại và Active</t>
   </si>
   <si>
-    <t>1. Nhập username đúng2. Nhập password sai3. Nhấn Login</t>
-  </si>
-  <si>
     <t>HTTP 401; không tạo token</t>
   </si>
   <si>
@@ -998,60 +947,33 @@
     <t>Đang ở Login</t>
   </si>
   <si>
-    <t>1. Để trống username2. Nhập password3. Nhấn Login</t>
-  </si>
-  <si>
-    <t>Username: emptyPassword: Password@123</t>
-  </si>
-  <si>
     <t>HTTP 400; yêu cầu nhập username</t>
   </si>
   <si>
     <t>Password để trống</t>
   </si>
   <si>
-    <t>1. Nhập username2. Để trống password3. Nhấn Login</t>
-  </si>
-  <si>
-    <t>Username: user01Password: empty</t>
-  </si>
-  <si>
     <t>HTTP 400; yêu cầu nhập password</t>
   </si>
   <si>
     <t>Username và password đều để trống</t>
   </si>
   <si>
-    <t>1. Không nhập username2. Không nhập password3. Nhấn Login</t>
-  </si>
-  <si>
-    <t>Username: emptyPassword: empty</t>
-  </si>
-  <si>
     <t>Username có giá trị null</t>
   </si>
   <si>
     <t>API Login hoạt động</t>
   </si>
   <si>
-    <t>1. Gửi request Login2. Truyền username=null</t>
-  </si>
-  <si>
     <t>HTTP 400; không authentication</t>
   </si>
   <si>
     <t>Password có giá trị null</t>
   </si>
   <si>
-    <t>1. Gửi request Login2. Truyền password=null</t>
-  </si>
-  <si>
     <t>Request Login có body null</t>
   </si>
   <si>
-    <t>1. Gửi request Login2. Không truyền body</t>
-  </si>
-  <si>
     <t>HTTP 400; server không crash</t>
   </si>
   <si>
@@ -1061,9 +983,6 @@
     <t>Tài khoản Active</t>
   </si>
   <si>
-    <t>1. Nhập username đúng2. Nhập password khác hoa/thường3. Nhấn Login</t>
-  </si>
-  <si>
     <t>HTTP 401 nếu password đúng là Password@123</t>
   </si>
   <si>
@@ -1073,9 +992,6 @@
     <t>User đã đăng nhập</t>
   </si>
   <si>
-    <t>1. Đăng nhập2. Chọn Logout3. Xác nhận</t>
-  </si>
-  <si>
     <t>Authorization: Bearer valid-token</t>
   </si>
   <si>
@@ -1088,9 +1004,6 @@
     <t>User chưa đăng nhập</t>
   </si>
   <si>
-    <t>1. Thực hiện Logout2. Không gửi token</t>
-  </si>
-  <si>
     <t>Authorization: empty</t>
   </si>
   <si>
@@ -1100,18 +1013,12 @@
     <t>Logout bằng token không hợp lệ hoặc hết hạn</t>
   </si>
   <si>
-    <t>1. Thực hiện Logout2. Gửi token sai/hết hạn</t>
-  </si>
-  <si>
     <t>Token: invalid/expired</t>
   </si>
   <si>
     <t>HTTP 401; không xử lý request</t>
   </si>
   <si>
-    <t>1. Sử dụng token ở giới hạn hợp lệ2. Logout</t>
-  </si>
-  <si>
     <t>Token: boundary length</t>
   </si>
   <si>
@@ -1121,9 +1028,6 @@
     <t>Authorization rỗng hoặc null</t>
   </si>
   <si>
-    <t>1. Gửi Logout2. Bỏ Authorization hoặc truyền null</t>
-  </si>
-  <si>
     <t>Authorization: empty/null</t>
   </si>
   <si>
@@ -1136,12 +1040,6 @@
     <t>Customer đã đăng nhập; vehicle type hợp lệ</t>
   </si>
   <si>
-    <t>1. Mở Đặt xe2. Nhập điểm đón3. Nhập điểm đến4. Chọn loại xe5. Nhấn Đặt xe</t>
-  </si>
-  <si>
-    <t>Pickup: 10.7769,106.7009Destination: 10.8000,106.6500Vehicle: CAR_4_SEATS</t>
-  </si>
-  <si>
     <t>Tạo booking thành công; sinh ID duy nhất; status SEARCHING_DRIVER</t>
   </si>
   <si>
@@ -1151,51 +1049,27 @@
     <t>Customer đã đăng nhập</t>
   </si>
   <si>
-    <t>1. Mở Đặt xe2. Lần lượt bỏ pickup/destination/vehicle type3. Nhấn Đặt xe</t>
-  </si>
-  <si>
     <t>Pickup/destination/vehicleTypeId: empty</t>
   </si>
   <si>
     <t>Tọa độ nằm tại giá trị biên hợp lệ</t>
   </si>
   <si>
-    <t>1. Nhập tọa độ biên2. Nhập destination3. Chọn xe4. Đặt xe</t>
-  </si>
-  <si>
-    <t>Latitude: ±90Longitude: ±180</t>
-  </si>
-  <si>
     <t>Chấp nhận tọa độ hợp lệ; booking được tạo</t>
   </si>
   <si>
-    <t>1. Nhập pickup sai2. Nhập destination3. Đặt xe</t>
-  </si>
-  <si>
-    <t>Latitude: nullLongitude: abc</t>
-  </si>
-  <si>
     <t>Tạo booking khi chưa đăng nhập</t>
   </si>
   <si>
-    <t>1. Nhập thông tin booking2. Nhấn Đặt xe</t>
-  </si>
-  <si>
     <t>Booking B001 tồn tại; user có quyền</t>
   </si>
   <si>
-    <t>1. Mở tra cứu booking2. Nhập ID3. Xem</t>
-  </si>
-  <si>
     <t>Booking ID: B001</t>
   </si>
   <si>
     <t>HTTP 200; hiển thị đúng thông tin booking</t>
   </si>
   <si>
-    <t>1. Nhập booking ID2. Tra cứu</t>
-  </si>
-  <si>
     <t>Booking ID: B999999</t>
   </si>
   <si>
@@ -1205,9 +1079,6 @@
     <t>Tra cứu booking với ID rỗng/null</t>
   </si>
   <si>
-    <t>1. Mở tra cứu2. Không nhập ID3. Tìm kiếm</t>
-  </si>
-  <si>
     <t>Booking ID: empty/null</t>
   </si>
   <si>
@@ -1217,24 +1088,15 @@
     <t>Xem booking khi chưa có token</t>
   </si>
   <si>
-    <t>1. Mở tra cứu booking2. Không đăng nhập</t>
-  </si>
-  <si>
     <t>Booking SEARCHING_DRIVER; driver AVAILABLE</t>
   </si>
   <si>
-    <t>1. Tạo booking2. Bắt đầu tìm driver3. Kiểm tra kết quả</t>
-  </si>
-  <si>
     <t>B001D01: AVAILABLEVehicle: CAR_4_SEATS</t>
   </si>
   <si>
     <t>Driver phù hợp được chọn; assignment được ghi nhận</t>
   </si>
   <si>
-    <t>1. Tạo booking2. Bắt đầu matching3. Chờ kết quả</t>
-  </si>
-  <si>
     <t>Suitable driver: 0</t>
   </si>
   <si>
@@ -1244,9 +1106,6 @@
     <t>Driver không đúng loại xe</t>
   </si>
   <si>
-    <t>1. Tạo booking2. Matching3. Kiểm tra driver</t>
-  </si>
-  <si>
     <t>Booking: CAR_4_SEATSD01: BIKE</t>
   </si>
   <si>
@@ -1256,9 +1115,6 @@
     <t>Driver BUSY/OFFLINE không được matching</t>
   </si>
   <si>
-    <t>1. Tạo booking2. Matching3. Kiểm tra kết quả</t>
-  </si>
-  <si>
     <t>D01: BUSYD02: OFFLINED03: AVAILABLE</t>
   </si>
   <si>
@@ -1268,69 +1124,36 @@
     <t>Ưu tiên driver phù hợp ở gần</t>
   </si>
   <si>
-    <t>1. Tạo booking2. Matching3. So sánh khoảng cách</t>
-  </si>
-  <si>
-    <t>D01: 1 kmD02: 5 kmCùng vehicle type</t>
-  </si>
-  <si>
     <t>Driver phù hợp và gần hơn được ưu tiên</t>
   </si>
   <si>
-    <t>1. Mở booking2. Chọn tìm driver</t>
-  </si>
-  <si>
     <t>B002: COMPLETED</t>
   </si>
   <si>
     <t>Booking đã gửi cho D01</t>
   </si>
   <si>
-    <t>1. D01 mở yêu cầu2. Chọn Chấp nhận</t>
-  </si>
-  <si>
-    <t>Booking: B001Driver: D01</t>
-  </si>
-  <si>
     <t>Accept thành công; trip được tạo/gán D01</t>
   </si>
   <si>
     <t>Booking đã được gửi cho D01</t>
   </si>
   <si>
-    <t>1. D02 mở booking2. Chọn Chấp nhận</t>
-  </si>
-  <si>
-    <t>Booking: B001Assigned: D01Current: D02</t>
-  </si>
-  <si>
     <t>Booking đã assigned D01</t>
   </si>
   <si>
     <t>1. Driver D02 chọn Chấp nhận</t>
   </si>
   <si>
-    <t>Booking: B001D01: assignedD02: accept</t>
-  </si>
-  <si>
     <t>HTTP 409; không tạo assignment thứ hai</t>
   </si>
   <si>
-    <t>1. D01 mở yêu cầu2. Chọn Từ chối</t>
-  </si>
-  <si>
     <t>HTTP 204; D01 bị loại; hệ thống có thể tìm driver khác</t>
   </si>
   <si>
     <t>Booking đã Accepted/Completed</t>
   </si>
   <si>
-    <t>1. Driver mở booking2. Chọn Từ chối</t>
-  </si>
-  <si>
-    <t>Booking: B001Status: COMPLETED</t>
-  </si>
-  <si>
     <t>HTTP 409; trạng thái không đổi</t>
   </si>
   <si>
@@ -1343,12 +1166,6 @@
     <t>Booking service/matching service có thể lỗi</t>
   </si>
   <si>
-    <t>1. Tạo booking2. Bắt đầu matching3. Mô phỏng lỗi service</t>
-  </si>
-  <si>
-    <t>Booking: B001Service: unavailable</t>
-  </si>
-  <si>
     <t>Trả lỗi phù hợp; không tạo dữ liệu sai; server không crash</t>
   </si>
   <si>
@@ -1358,9 +1175,6 @@
     <t>User có quyền quản lý driver</t>
   </si>
   <si>
-    <t>1. Mở Driver Management2. Chọn xem tất cả</t>
-  </si>
-  <si>
     <t>Filter: none</t>
   </si>
   <si>
@@ -1370,9 +1184,6 @@
     <t>Lọc driver theo AVAILABLE</t>
   </si>
   <si>
-    <t>1. Mở danh sách2. Chọn status AVAILABLE3. Tìm kiếm</t>
-  </si>
-  <si>
     <t>Status: AVAILABLE</t>
   </si>
   <si>
@@ -1382,9 +1193,6 @@
     <t>Lọc driver theo vehicle type</t>
   </si>
   <si>
-    <t>1. Mở danh sách2. Chọn vehicle type3. Tìm kiếm</t>
-  </si>
-  <si>
     <t>Vehicle Type: CAR_4_SEATS</t>
   </si>
   <si>
@@ -1394,24 +1202,12 @@
     <t>Lọc driver với status không hợp lệ</t>
   </si>
   <si>
-    <t>1. Chọn filter status2. Nhập giá trị không hợp lệ3. Tìm kiếm</t>
-  </si>
-  <si>
     <t>Status: INVALID</t>
   </si>
   <si>
     <t>HTTP 400; không trả dữ liệu sai</t>
   </si>
   <si>
-    <t>1. Mở driver2. Chọn Edit3. Sửa thông tin4. Lưu</t>
-  </si>
-  <si>
-    <t>Driver: D01Thông tin hợp lệ</t>
-  </si>
-  <si>
-    <t>1. Nhập driver ID2. Cập nhật</t>
-  </si>
-  <si>
     <t>Driver ID: D999999</t>
   </si>
   <si>
@@ -1421,75 +1217,45 @@
     <t>Cập nhật driver với body rỗng/null</t>
   </si>
   <si>
-    <t>1. Mở Edit2. Không nhập dữ liệu3. Lưu</t>
-  </si>
-  <si>
     <t>Body: empty/null</t>
   </si>
   <si>
     <t>Customer cố cập nhật driver</t>
   </si>
   <si>
-    <t>1. Mở thông tin driver2. Chọn Edit3. Lưu</t>
-  </si>
-  <si>
-    <t>Role: CUSTOMERDriver: D01</t>
-  </si>
-  <si>
     <t>HTTP 403; dữ liệu không đổi</t>
   </si>
   <si>
     <t>Chuyển driver sang AVAILABLE</t>
   </si>
   <si>
-    <t>1. Mở trạng thái2. Chọn AVAILABLE3. Lưu</t>
-  </si>
-  <si>
     <t>Cập nhật thành công</t>
   </si>
   <si>
     <t>Chuyển driver sang BUSY</t>
   </si>
   <si>
-    <t>1. Mở trạng thái2. Chọn BUSY3. Lưu</t>
-  </si>
-  <si>
     <t>Status: BUSY</t>
   </si>
   <si>
     <t>Cập nhật status không hợp lệ</t>
   </si>
   <si>
-    <t>1. Chọn status2. Nhập giá trị ngoài enum3. Lưu</t>
-  </si>
-  <si>
     <t>HTTP 400; status cũ giữ nguyên</t>
   </si>
   <si>
     <t>Cập nhật status rỗng/null</t>
   </si>
   <si>
-    <t>1. Không chọn status2. Lưu</t>
-  </si>
-  <si>
     <t>Status: empty/null</t>
   </si>
   <si>
     <t>Driver đã đăng nhập</t>
   </si>
   <si>
-    <t>1. Mở cập nhật vị trí2. Nhập latitude/longitude3. Lưu</t>
-  </si>
-  <si>
-    <t>Latitude: 10.7769Longitude: 106.7009</t>
-  </si>
-  <si>
     <t>Latitude tại giá trị biên</t>
   </si>
   <si>
-    <t>1. Nhập latitude biên2. Nhập longitude3. Lưu</t>
-  </si>
-  <si>
     <t>Latitude: 90 hoặc -90</t>
   </si>
   <si>
@@ -1499,45 +1265,24 @@
     <t>Longitude tại giá trị biên</t>
   </si>
   <si>
-    <t>1. Nhập longitude biên2. Lưu</t>
-  </si>
-  <si>
     <t>Longitude: 180 hoặc -180</t>
   </si>
   <si>
     <t>Thiếu latitude hoặc longitude</t>
   </si>
   <si>
-    <t>1. Mở cập nhật vị trí2. Bỏ một hoặc cả hai tọa độ3. Lưu</t>
-  </si>
-  <si>
-    <t>Latitude: nullLongitude: null</t>
-  </si>
-  <si>
     <t>HTTP 400; vị trí cũ giữ nguyên</t>
   </si>
   <si>
     <t>Tọa độ vượt miền cho phép</t>
   </si>
   <si>
-    <t>1. Nhập tọa độ vượt giới hạn2. Lưu</t>
-  </si>
-  <si>
-    <t>Latitude: 91Longitude: 181</t>
-  </si>
-  <si>
     <t>Xử lý ngoại lệ khi cập nhật driver</t>
   </si>
   <si>
     <t>Driver service/database lỗi</t>
   </si>
   <si>
-    <t>1. Thực hiện cập nhật2. Mô phỏng lỗi service3. Kiểm tra kết quả</t>
-  </si>
-  <si>
-    <t>Driver: D01Service: unavailable</t>
-  </si>
-  <si>
     <t>Trả lỗi có kiểm soát; server không crash</t>
   </si>
   <si>
@@ -1547,9 +1292,6 @@
     <t>Trip đã assign driver</t>
   </si>
   <si>
-    <t>1. Driver mở trip2. Chọn Arrived3. Xác nhận</t>
-  </si>
-  <si>
     <t>T001ASSIGNED → ARRIVED</t>
   </si>
   <si>
@@ -1562,9 +1304,6 @@
     <t>Trip đang ASSIGNED</t>
   </si>
   <si>
-    <t>1. Chuyển ARRIVED2. Chuyển PICKED_UP3. Chuyển IN_PROGRESS4. Chuyển COMPLETED</t>
-  </si>
-  <si>
     <t>ASSIGNED → ARRIVED → PICKED_UP → IN_PROGRESS → COMPLETED</t>
   </si>
   <si>
@@ -1574,54 +1313,30 @@
     <t>Bỏ qua trạng thái trong chuỗi trip</t>
   </si>
   <si>
-    <t>1. Mở trip2. Chọn IN_PROGRESS3. Xác nhận</t>
-  </si>
-  <si>
     <t>Không cho phép; HTTP 400/409</t>
   </si>
   <si>
     <t>Trip được assign D01</t>
   </si>
   <si>
-    <t>1. D01 mở trip2. Cập nhật status</t>
-  </si>
-  <si>
-    <t>Driver: D01Trip: T001</t>
-  </si>
-  <si>
     <t>Trip assign D01</t>
   </si>
   <si>
-    <t>1. D02 mở T0012. Cập nhật status</t>
-  </si>
-  <si>
     <t>Driver: D02Trip: T001</t>
   </si>
   <si>
-    <t>1. Nhập trip ID2. Chọn status3. Lưu</t>
-  </si>
-  <si>
     <t>Trip: T999999</t>
   </si>
   <si>
-    <t>1. Mở Trip2. Nhập ID3. Xem</t>
-  </si>
-  <si>
     <t>Trip: T001</t>
   </si>
   <si>
     <t>HTTP 200; hiển thị đúng thông tin</t>
   </si>
   <si>
-    <t>1. Nhập trip ID2. Xem</t>
-  </si>
-  <si>
     <t>Xem trip đã hoàn thành</t>
   </si>
   <si>
-    <t>1. Mở trip2. Xem thông tin</t>
-  </si>
-  <si>
     <t>T001Status: COMPLETED</t>
   </si>
   <si>
@@ -1631,36 +1346,21 @@
     <t>Cập nhật trip với status rỗng/null</t>
   </si>
   <si>
-    <t>1. Mở cập nhật status2. Không chọn status3. Lưu</t>
-  </si>
-  <si>
     <t>Cập nhật trip với status không hợp lệ</t>
   </si>
   <si>
-    <t>1. Nhập status ngoài danh sách2. Lưu</t>
-  </si>
-  <si>
     <t>Status: CANCELLED</t>
   </si>
   <si>
     <t>User không phải assigned driver cập nhật trip</t>
   </si>
   <si>
-    <t>1. Đăng nhập user khác2. Mở T0013. Cập nhật</t>
-  </si>
-  <si>
     <t>Cập nhật trip ID không tồn tại</t>
   </si>
   <si>
-    <t>1. Nhập ID không tồn tại2. Cập nhật</t>
-  </si>
-  <si>
     <t>Xem lịch sử trip với phân trang mặc định</t>
   </si>
   <si>
-    <t>1. Mở Trip History2. Không nhập page/size</t>
-  </si>
-  <si>
     <t>Page: 0Size: 20</t>
   </si>
   <si>
@@ -1670,9 +1370,6 @@
     <t>History với page=0 và size=1</t>
   </si>
   <si>
-    <t>1. Mở history2. Nhập page=0,size=13. Tìm kiếm</t>
-  </si>
-  <si>
     <t>Page: 0Size: 1</t>
   </si>
   <si>
@@ -1682,9 +1379,6 @@
     <t>History với size tối đa</t>
   </si>
   <si>
-    <t>1. Mở history2. Nhập size=100</t>
-  </si>
-  <si>
     <t>Page: 0Size: 100</t>
   </si>
   <si>
@@ -1694,27 +1388,18 @@
     <t>History với size ngoài giới hạn</t>
   </si>
   <si>
-    <t>1. Nhập size=02. Thử lại size=101</t>
-  </si>
-  <si>
     <t>Size: 0 / 101</t>
   </si>
   <si>
     <t>Xem history khi chưa đăng nhập</t>
   </si>
   <si>
-    <t>1. Mở Trip History2. Không đăng nhập</t>
-  </si>
-  <si>
     <t>Rating với score nhỏ nhất</t>
   </si>
   <si>
     <t>Trip COMPLETED; customer là chủ trip</t>
   </si>
   <si>
-    <t>1. Mở Rating2. Chọn 1 sao3. Gửi</t>
-  </si>
-  <si>
     <t>Score: 1Comment: Good</t>
   </si>
   <si>
@@ -1724,18 +1409,12 @@
     <t>Rating với score lớn nhất</t>
   </si>
   <si>
-    <t>1. Mở Rating2. Chọn 5 sao3. Gửi</t>
-  </si>
-  <si>
     <t>Score: 5Comment: Excellent</t>
   </si>
   <si>
     <t>Rating với score ngoài khoảng</t>
   </si>
   <si>
-    <t>1. Nhập score2. Gửi</t>
-  </si>
-  <si>
     <t>Score: 0 / 6</t>
   </si>
   <si>
@@ -1745,21 +1424,12 @@
     <t>Rating không có score</t>
   </si>
   <si>
-    <t>1. Mở Rating2. Không chọn score3. Gửi</t>
-  </si>
-  <si>
     <t>Score: emptyComment: Good</t>
   </si>
   <si>
     <t>HTTP 400; không tạo rating</t>
   </si>
   <si>
-    <t>1. Mở trip2. Chọn Rating3. Gửi</t>
-  </si>
-  <si>
-    <t>Status: IN_PROGRESSScore: 5</t>
-  </si>
-  <si>
     <t>HTTP 409; không tạo rating</t>
   </si>
   <si>
@@ -1769,24 +1439,12 @@
     <t>Trip thuộc C01</t>
   </si>
   <si>
-    <t>1. C02 mở T0012. Chọn Rating3. Gửi</t>
-  </si>
-  <si>
-    <t>Owner: C01Current: C02Score: 5</t>
-  </si>
-  <si>
     <t>HTTP 403; không tạo rating</t>
   </si>
   <si>
     <t>Trip đã có rating</t>
   </si>
   <si>
-    <t>1. Mở trip2. Chọn Rating3. Gửi lần 2</t>
-  </si>
-  <si>
-    <t>Trip: T001Score: 4</t>
-  </si>
-  <si>
     <t>HTTP 409; không tạo rating duplicate</t>
   </si>
   <si>
@@ -1796,30 +1454,18 @@
     <t>Trip service/database lỗi</t>
   </si>
   <si>
-    <t>1. Mở trip2. Cập nhật status3. Mô phỏng lỗi service</t>
-  </si>
-  <si>
     <t>T001Service: unavailable</t>
   </si>
   <si>
     <t>Trả lỗi có kiểm soát; không làm sai trạng thái trip</t>
   </si>
   <si>
-    <t>1. Mở Payment2. Chọn Cash3. Xác nhận</t>
-  </si>
-  <si>
-    <t>Trip: T001Method: CASH</t>
-  </si>
-  <si>
     <t>Thanh toán thành công; HTTP 201</t>
   </si>
   <si>
     <t>Thanh toán bằng ELECTRONIC</t>
   </si>
   <si>
-    <t>1. Mở Payment2. Chọn Electronic3. Xác nhận</t>
-  </si>
-  <si>
     <t>Method: ELECTRONIC</t>
   </si>
   <si>
@@ -1829,60 +1475,33 @@
     <t>Thanh toán với method không hợp lệ</t>
   </si>
   <si>
-    <t>1. Chọn phương thức2. Gửi thanh toán</t>
-  </si>
-  <si>
     <t>Method: BANK_TRANSFER</t>
   </si>
   <si>
     <t>Không nhập payment method</t>
   </si>
   <si>
-    <t>1. Mở Payment2. Không chọn method3. Xác nhận</t>
-  </si>
-  <si>
     <t>Method: empty/null</t>
   </si>
   <si>
     <t>Thanh toán khi trip chưa hoàn thành</t>
   </si>
   <si>
-    <t>1. Mở Payment2. Chọn CASH3. Thanh toán</t>
-  </si>
-  <si>
-    <t>Trip: T001Status: IN_PROGRESSMethod: CASH</t>
-  </si>
-  <si>
     <t>Không lưu thông tin thẻ nhạy cảm</t>
   </si>
   <si>
     <t>Electronic payment hoạt động</t>
   </si>
   <si>
-    <t>1. Thực hiện payment2. Gửi thêm card number/CVV3. Kiểm tra response/database</t>
-  </si>
-  <si>
-    <t>Card Number: test-card-numberCVV: 123</t>
-  </si>
-  <si>
     <t>Không lưu hoặc trả dữ liệu thẻ nhạy cảm</t>
   </si>
   <si>
     <t>Webhook báo SUCCESS</t>
   </si>
   <si>
-    <t>1. Gửi webhook2. Kiểm tra payment</t>
-  </si>
-  <si>
-    <t>Payment ID: P001Status: SUCCESS</t>
-  </si>
-  <si>
     <t>Webhook báo FAILED</t>
   </si>
   <si>
-    <t>Payment ID: P001Status: FAILED</t>
-  </si>
-  <si>
     <t>HTTP 200; payment chuyển FAILED</t>
   </si>
   <si>
@@ -1892,21 +1511,12 @@
     <t>API webhook hoạt động</t>
   </si>
   <si>
-    <t>1. Gửi webhook2. Bỏ từng trường bắt buộc</t>
-  </si>
-  <si>
-    <t>PaymentId: emptyStatus: SUCCESS</t>
-  </si>
-  <si>
     <t>HTTP 400; không cập nhật payment sai</t>
   </si>
   <si>
     <t>Webhook với status không hợp lệ</t>
   </si>
   <si>
-    <t>1. Gửi webhook2. Nhập status ngoài enum</t>
-  </si>
-  <si>
     <t>Status: PENDING</t>
   </si>
   <si>
@@ -1916,24 +1526,12 @@
     <t>Payment P001 FAILED</t>
   </si>
   <si>
-    <t>1. Mở payment2. Chọn Retry</t>
-  </si>
-  <si>
-    <t>Payment: P001Status: FAILED</t>
-  </si>
-  <si>
     <t>Retry thành công; HTTP 200</t>
   </si>
   <si>
     <t>Payment P001 SUCCESS</t>
   </si>
   <si>
-    <t>Payment: P001Status: SUCCESS</t>
-  </si>
-  <si>
-    <t>1. Nhập payment ID2. Chọn Retry</t>
-  </si>
-  <si>
     <t>Payment: P999999</t>
   </si>
   <si>
@@ -1943,9 +1541,6 @@
     <t>Retry với paymentId rỗng/null</t>
   </si>
   <si>
-    <t>1. Chọn Retry2. Bỏ payment ID</t>
-  </si>
-  <si>
     <t>Payment ID: empty/null</t>
   </si>
   <si>
@@ -1958,9 +1553,6 @@
     <t>Payment provider hoạt động</t>
   </si>
   <si>
-    <t>1. Nhập dữ liệu tại giới hạn2. Thực hiện payment</t>
-  </si>
-  <si>
     <t>ProviderTransactionId tại min/max length</t>
   </si>
   <si>
@@ -1979,9 +1571,6 @@
     <t>User đã login; có notification</t>
   </si>
   <si>
-    <t>1. Mở Notifications2. Xem danh sách</t>
-  </si>
-  <si>
     <t>User: U01N01,N02</t>
   </si>
   <si>
@@ -2015,9 +1604,6 @@
     <t>Xem notification khi chưa đăng nhập</t>
   </si>
   <si>
-    <t>1. Mở Notifications2. Không đăng nhập</t>
-  </si>
-  <si>
     <t>TC-NOTI-004</t>
   </si>
   <si>
@@ -2027,9 +1613,6 @@
     <t>Notification tồn tại và unread</t>
   </si>
   <si>
-    <t>1. Mở notification2. Chọn Mark as Read</t>
-  </si>
-  <si>
     <t>Notification: N001Read: false</t>
   </si>
   <si>
@@ -2042,9 +1625,6 @@
     <t>Đánh dấu notification không tồn tại</t>
   </si>
   <si>
-    <t>1. Nhập notification ID2. Mark as Read</t>
-  </si>
-  <si>
     <t>N999999</t>
   </si>
   <si>
@@ -2054,9 +1634,6 @@
     <t>Notification ID rỗng/null</t>
   </si>
   <si>
-    <t>1. Chọn Mark as Read2. Không nhập ID</t>
-  </si>
-  <si>
     <t>ID: empty/null</t>
   </si>
   <si>
@@ -2072,18 +1649,12 @@
     <t>Notification service lỗi</t>
   </si>
   <si>
-    <t>1. Mở Notifications2. Mô phỏng lỗi service</t>
-  </si>
-  <si>
     <t>Service: unavailable</t>
   </si>
   <si>
     <t>User có quyền Operation</t>
   </si>
   <si>
-    <t>1. Đăng nhập2. Mở Operations3. Chọn Active Trips</t>
-  </si>
-  <si>
     <t>Role: OPERATION</t>
   </si>
   <si>
@@ -2093,9 +1664,6 @@
     <t>Customer truy cập active trips</t>
   </si>
   <si>
-    <t>1. Mở Operations2. Chọn Active Trips</t>
-  </si>
-  <si>
     <t>Role: CUSTOMER</t>
   </si>
   <si>
@@ -2117,9 +1685,6 @@
     <t>Operation staff xem abnormal trips</t>
   </si>
   <si>
-    <t>1. Mở Operations2. Chọn Abnormal Trips</t>
-  </si>
-  <si>
     <t>HTTP 200; chỉ hiển thị trip ABNORMAL</t>
   </si>
   <si>
@@ -2132,45 +1697,21 @@
     <t>Abnormal trips: 0</t>
   </si>
   <si>
-    <t>1. Mở trip2. Chọn Resolve3. Nhập resolution4. Nhập note5. Xác nhận</t>
-  </si>
-  <si>
-    <t>Trip: T001Resolution: REFUNDNote: Customer refund</t>
-  </si>
-  <si>
     <t>Resolve thành công; cập nhật trip; ghi audit log</t>
   </si>
   <si>
     <t>User không đủ quyền resolve trip</t>
   </si>
   <si>
-    <t>1. Mở trip2. Chọn Resolve3. Xác nhận</t>
-  </si>
-  <si>
-    <t>1. Nhập trip ID2. Resolve</t>
-  </si>
-  <si>
     <t>Resolve thiếu resolution hoặc note</t>
   </si>
   <si>
-    <t>1. Mở Resolve2. Bỏ resolution/note3. Xác nhận</t>
-  </si>
-  <si>
-    <t>Resolution: emptyNote: empty</t>
-  </si>
-  <si>
     <t>Resolve trip không ở trạng thái ABNORMAL</t>
   </si>
   <si>
-    <t>Trip: T001Status: COMPLETED</t>
-  </si>
-  <si>
     <t>HTTP 409; trạng thái giữ nguyên</t>
   </si>
   <si>
-    <t>1. Mở Transactions2. Chọn status SUCCESS</t>
-  </si>
-  <si>
     <t>Status: SUCCESS</t>
   </si>
   <si>
@@ -2180,33 +1721,18 @@
     <t>Lọc transaction theo khoảng thời gian</t>
   </si>
   <si>
-    <t>1. Mở Transactions2. Nhập from/to3. Tìm kiếm</t>
-  </si>
-  <si>
-    <t>From: 2026-01-01To: 2026-01-31</t>
-  </si>
-  <si>
     <t>Chỉ hiển thị dữ liệu trong khoảng</t>
   </si>
   <si>
     <t>Khoảng thời gian from lớn hơn to</t>
   </si>
   <si>
-    <t>1. Nhập from/to2. Tìm kiếm</t>
-  </si>
-  <si>
-    <t>From: 2026-02-01To: 2026-01-01</t>
-  </si>
-  <si>
     <t>HTTP 400 hoặc kết quả rỗng theo rule</t>
   </si>
   <si>
     <t>Xem transactions không có filter</t>
   </si>
   <si>
-    <t>1. Mở Transactions2. Không nhập filter</t>
-  </si>
-  <si>
     <t>Status/from/to: empty</t>
   </si>
   <si>
@@ -2219,12 +1745,6 @@
     <t>Kiểm tra giá trị biên của khoảng thời gian</t>
   </si>
   <si>
-    <t>1. Nhập from và to cùng ngày2. Tìm kiếm</t>
-  </si>
-  <si>
-    <t>From: 2026-01-01To: 2026-01-01</t>
-  </si>
-  <si>
     <t>Hệ thống xử lý đúng khoảng thời gian biên</t>
   </si>
   <si>
@@ -2234,69 +1754,39 @@
     <t>User có quyền Report</t>
   </si>
   <si>
-    <t>1. Mở Reports2. Chọn Trips3. Nhập from/to4. Xem</t>
-  </si>
-  <si>
     <t>HTTP 200; báo cáo đúng khoảng thời gian</t>
   </si>
   <si>
     <t>Xem báo cáo trong một ngày</t>
   </si>
   <si>
-    <t>1. Mở Trips Report2. Nhập cùng ngày3. Xem</t>
-  </si>
-  <si>
     <t>Báo cáo được tạo nếu one-day range hợp lệ</t>
   </si>
   <si>
     <t>Báo cáo thiếu from/to</t>
   </si>
   <si>
-    <t>1. Mở Report2. Bỏ from hoặc to3. Xem</t>
-  </si>
-  <si>
-    <t>From: emptyTo: 2026-01-31</t>
-  </si>
-  <si>
     <t>HTTP 400; không tạo báo cáo</t>
   </si>
   <si>
     <t>From lớn hơn To</t>
   </si>
   <si>
-    <t>1. Nhập khoảng thời gian2. Xem report</t>
-  </si>
-  <si>
     <t>Xem Revenue Report với khoảng thời gian hợp lệ</t>
   </si>
   <si>
-    <t>1. Mở Revenue Report2. Nhập from/to3. Xem</t>
-  </si>
-  <si>
     <t>Revenue Report trong một ngày</t>
   </si>
   <si>
-    <t>1. Mở Revenue Report2. Nhập cùng ngày3. Xem</t>
-  </si>
-  <si>
     <t>Báo cáo được tạo nếu range hợp lệ</t>
   </si>
   <si>
     <t>Revenue Report thiếu from/to</t>
   </si>
   <si>
-    <t>1. Mở Revenue Report2. Bỏ from/to3. Xem</t>
-  </si>
-  <si>
-    <t>From: emptyTo: empty</t>
-  </si>
-  <si>
     <t>Customer truy cập Report</t>
   </si>
   <si>
-    <t>1. Mở Reports2. Chọn Trips/Revenue</t>
-  </si>
-  <si>
     <t>HTTP 403; không trả dữ liệu báo cáo</t>
   </si>
   <si>
@@ -2306,15 +1796,6 @@
     <t>Report service/database lỗi</t>
   </si>
   <si>
-    <t>1. Nhập khoảng thời gian hợp lệ2. Xem report3. Mô phỏng lỗi</t>
-  </si>
-  <si>
-    <t>From: 2026-01-01To: 2026-01-31Service: unavailable</t>
-  </si>
-  <si>
-    <t>1. Mở Profile2. Chọn My Profile</t>
-  </si>
-  <si>
     <t>User: U01</t>
   </si>
   <si>
@@ -2324,24 +1805,12 @@
     <t>Xem profile khi chưa đăng nhập</t>
   </si>
   <si>
-    <t>1. Mở Profile2. Không đăng nhập</t>
-  </si>
-  <si>
     <t>Cập nhật thông tin cá nhân hợp lệ</t>
   </si>
   <si>
-    <t>1. Mở Profile2. Chọn Edit3. Sửa thông tin4. Lưu</t>
-  </si>
-  <si>
-    <t>Full Name: Nguyen Van BEmail: valid@example.com</t>
-  </si>
-  <si>
     <t>Cập nhật profile với email sai/body null</t>
   </si>
   <si>
-    <t>1. Mở Edit2. Nhập email sai hoặc body null3. Lưu</t>
-  </si>
-  <si>
     <t>Email: abc@ / Body: null</t>
   </si>
   <si>
@@ -2351,42 +1820,24 @@
     <t>Admin xem danh sách Customer</t>
   </si>
   <si>
-    <t>1. Mở Customer Management2. Xem danh sách</t>
-  </si>
-  <si>
-    <t>Page: 1PageSize: 20</t>
-  </si>
-  <si>
     <t>HTTP 200; hiển thị danh sách customer</t>
   </si>
   <si>
     <t>PageSize đạt giá trị tối đa</t>
   </si>
   <si>
-    <t>1. Mở danh sách Customer2. Nhập pageSize=100</t>
-  </si>
-  <si>
-    <t>Page: 1PageSize: 100</t>
-  </si>
-  <si>
     <t>Trả tối đa 100 customer</t>
   </si>
   <si>
     <t>PageSize ngoài giới hạn</t>
   </si>
   <si>
-    <t>1. Nhập pageSize=02. Thử lại pageSize=101</t>
-  </si>
-  <si>
     <t>PageSize: 0 / 101</t>
   </si>
   <si>
     <t>Tìm customer không có kết quả</t>
   </si>
   <si>
-    <t>1. Mở Customer Management2. Nhập keyword3. Tìm kiếm</t>
-  </si>
-  <si>
     <t>Keyword: notfoundxyz</t>
   </si>
   <si>
@@ -2396,9 +1847,6 @@
     <t>1. Mở Customer Management</t>
   </si>
   <si>
-    <t>1. Nhập user ID2. Xem</t>
-  </si>
-  <si>
     <t>User ID: C001</t>
   </si>
   <si>
@@ -2426,12 +1874,6 @@
     <t>User service/database lỗi</t>
   </si>
   <si>
-    <t>1. Thực hiện truy vấn/update user2. Mô phỏng lỗi</t>
-  </si>
-  <si>
-    <t>User: U01Service: unavailable</t>
-  </si>
-  <si>
     <t>Trả lỗi phù hợp; không crash; dữ liệu không sai</t>
   </si>
   <si>
@@ -2444,9 +1886,6 @@
     <t>Xem danh sách vehicle</t>
   </si>
   <si>
-    <t>1. Mở Vehicle Management2. Xem danh sách</t>
-  </si>
-  <si>
     <t>Authorization: valid</t>
   </si>
   <si>
@@ -2474,63 +1913,30 @@
     <t>Driver và vehicle type tồn tại; user có quyền</t>
   </si>
   <si>
-    <t>1. Mở Add Vehicle2. Chọn driver3. Chọn vehicle type4. Nhập biển số5. Lưu</t>
-  </si>
-  <si>
-    <t>Driver: D01Vehicle: CAR_4_SEATSPlate: 51A-12345</t>
-  </si>
-  <si>
     <t>Tạo vehicle thiếu trường bắt buộc</t>
   </si>
   <si>
-    <t>1. Mở Add Vehicle2. Lần lượt bỏ driver/type/plate3. Lưu</t>
-  </si>
-  <si>
-    <t>DriverId/VehicleTypeId/PlateNumber: empty</t>
-  </si>
-  <si>
     <t>Plate number rỗng hoặc sai định dạng</t>
   </si>
   <si>
-    <t>1. Mở Add Vehicle2. Nhập biển số sai3. Lưu</t>
-  </si>
-  <si>
     <t>Plate: empty / ABC123XYZ</t>
   </si>
   <si>
     <t>HTTP 400 nếu không đúng format</t>
   </si>
   <si>
-    <t>1. Mở Add Vehicle2. Nhập thông tin3. Lưu</t>
-  </si>
-  <si>
-    <t>1. Mở vehicle2. Chọn Edit3. Sửa thông tin4. Lưu</t>
-  </si>
-  <si>
-    <t>Vehicle: V001Plate: 51A-99999</t>
-  </si>
-  <si>
     <t>HTTP 200; vehicle được cập nhật</t>
   </si>
   <si>
-    <t>1. Nhập vehicle ID2. Cập nhật</t>
-  </si>
-  <si>
     <t>Vehicle: V999999</t>
   </si>
   <si>
     <t>Cập nhật vehicle với body null</t>
   </si>
   <si>
-    <t>1. Gửi update2. Không truyền body</t>
-  </si>
-  <si>
     <t>Kiểm tra giá trị biên của plate number</t>
   </si>
   <si>
-    <t>1. Nhập plate tại giới hạn cho phép2. Lưu3. Thử vượt giới hạn</t>
-  </si>
-  <si>
     <t>Plate: min/max length</t>
   </si>
   <si>
@@ -2543,13 +1949,946 @@
     <t>Vehicle/database service lỗi</t>
   </si>
   <si>
-    <t>1. Tạo/update vehicle2. Mô phỏng lỗi service</t>
-  </si>
-  <si>
-    <t>Vehicle: V001Service: unavailable</t>
-  </si>
-  <si>
     <t>Trả lỗi có kiểm soát; không tạo/update sai</t>
+  </si>
+  <si>
+    <t>1. Mở Register
+2. Nhập username
+3. Nhập password
+4. Nhập họ tên, phone, email
+5. Nhấn Register</t>
+  </si>
+  <si>
+    <t>Username: customer01
+Password: Password123!
+Full Name: Nguyen Van A
+Phone: 0901234567
+Email: customer01@example.com</t>
+  </si>
+  <si>
+    <t>1. Mở Register
+2. Lần lượt bỏ từng trường bắt buộc
+3. Nhấn Register</t>
+  </si>
+  <si>
+    <t>1. Mở Register
+2. Nhập dữ liệu trùng
+3. Nhấn Register</t>
+  </si>
+  <si>
+    <t>1. Nhập thông tin đăng ký
+2. Nhập email sai format
+3. Nhấn Register</t>
+  </si>
+  <si>
+    <t>1. Mở chức năng Register
+2. Gửi body rỗng/null hoặc JSON sai cấu trúc</t>
+  </si>
+  <si>
+    <t>1. Nhập dữ liệu tại giới hạn dưới
+2. Đăng ký
+3. Nhập dữ liệu tại giới hạn trên
+4. Đăng ký</t>
+  </si>
+  <si>
+    <t>1. Nhập dữ liệu hợp lệ
+2. Nhấn Register
+3. Mô phỏng lỗi service/database</t>
+  </si>
+  <si>
+    <t>Username: customer01
+Email: customer01@example.com
+Phone: 0901234567</t>
+  </si>
+  <si>
+    <t>1. Mở Login
+2. Nhập username
+3. Nhập password
+4. Nhấn Login</t>
+  </si>
+  <si>
+    <t>1. Nhập username đúng
+2. Nhập password sai
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>1. Để trống username
+2. Nhập password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>1. Nhập username
+2. Để trống password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>1. Không nhập username
+2. Không nhập password
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login
+2. Truyền username=null</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login
+2. Truyền password=null</t>
+  </si>
+  <si>
+    <t>1. Gửi request Login
+2. Không truyền body</t>
+  </si>
+  <si>
+    <t>1. Nhập username đúng
+2. Nhập password khác hoa/thường
+3. Nhấn Login</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Username: unknown01
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: Wrong@123</t>
+  </si>
+  <si>
+    <t>Username: empty
+Password: Password@123</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: empty</t>
+  </si>
+  <si>
+    <t>Username: empty
+Password: empty</t>
+  </si>
+  <si>
+    <t>Username: nul
+lPassword: Password@123</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: null</t>
+  </si>
+  <si>
+    <t>Username: user01
+Password: password@123</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập
+2. Chọn Logout
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Thực hiện Logout
+2. Không gửi token</t>
+  </si>
+  <si>
+    <t>1. Thực hiện Logout
+2. Gửi token sai/hết hạn</t>
+  </si>
+  <si>
+    <t>1. Sử dụng token ở giới hạn hợp lệ
+2. Logout</t>
+  </si>
+  <si>
+    <t>1. Gửi Logout
+2. Bỏ Authorization hoặc truyền null</t>
+  </si>
+  <si>
+    <t>1. Mở Đặt xe
+2. Nhập điểm đón
+3. Nhập điểm đến
+4. Chọn loại xe
+5. Nhấn Đặt xe</t>
+  </si>
+  <si>
+    <t>1. Mở Đặt xe
+2. Lần lượt bỏ pickup/destination/vehicle type
+3. Nhấn Đặt xe</t>
+  </si>
+  <si>
+    <t>1. Nhập tọa độ biên
+2. Nhập destination
+3. Chọn xe
+4. Đặt xe</t>
+  </si>
+  <si>
+    <t>1. Nhập pickup sai
+2. Nhập destination
+3. Đặt xe</t>
+  </si>
+  <si>
+    <t>1. Nhập thông tin booking
+2. Nhấn Đặt xe</t>
+  </si>
+  <si>
+    <t>1. Mở tra cứu booking
+2. Nhập ID
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Nhập booking ID
+2. Tra cứu</t>
+  </si>
+  <si>
+    <t>1. Mở tra cứu
+2. Không nhập ID
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Mở tra cứu booking
+2. Không đăng nhập</t>
+  </si>
+  <si>
+    <t>1. Tạo booking
+2. Bắt đầu tìm driver
+3. Kiểm tra kết quả</t>
+  </si>
+  <si>
+    <t>1. Tạo booking
+2. Bắt đầu matching
+3. Chờ kết quả</t>
+  </si>
+  <si>
+    <t>1. Tạo booking
+2. Matching
+3. Kiểm tra driver</t>
+  </si>
+  <si>
+    <t>1. Tạo booking
+2. Matching
+3. Kiểm tra kết quả</t>
+  </si>
+  <si>
+    <t>1. Tạo booking
+2. Matching
+3. So sánh khoảng cách</t>
+  </si>
+  <si>
+    <t>1. Mở booking
+2. Chọn tìm driver</t>
+  </si>
+  <si>
+    <t>1. D01 mở yêu cầu
+2. Chọn Chấp nhận</t>
+  </si>
+  <si>
+    <t>1. D02 mở booking
+2. Chọn Chấp nhận</t>
+  </si>
+  <si>
+    <t>1. D01 mở yêu cầu
+2. Chọn Từ chối</t>
+  </si>
+  <si>
+    <t>1. Driver mở booking
+2. Chọn Từ chối</t>
+  </si>
+  <si>
+    <t>1. Tạo booking
+2. Bắt đầu matching
+3. Mô phỏng lỗi service</t>
+  </si>
+  <si>
+    <t>Pickup: 10.7769,106.7009
+Destination: 10.8000,106.6500
+Vehicle: CAR_4_SEATS</t>
+  </si>
+  <si>
+    <t>Latitude: ±90
+Longitude: ±180</t>
+  </si>
+  <si>
+    <t>Latitude: null
+Longitude: abc</t>
+  </si>
+  <si>
+    <t>D01: 1 km
+D02: 5 km
+Cùng vehicle type</t>
+  </si>
+  <si>
+    <t>Booking: B001
+Driver: D01</t>
+  </si>
+  <si>
+    <t>Booking: B001
+Assigned: D01
+Current: D02</t>
+  </si>
+  <si>
+    <t>Booking: B001
+D01: assigned
+D02: accept</t>
+  </si>
+  <si>
+    <t>Booking: B001
+Status: COMPLETED</t>
+  </si>
+  <si>
+    <t>Booking: B001
+Service: unavailable</t>
+  </si>
+  <si>
+    <t>1. Mở Driver Management
+2. Chọn xem tất cả</t>
+  </si>
+  <si>
+    <t>1. Mở danh sách
+2. Chọn status AVAILABLE
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Mở danh sách
+2. Chọn vehicle type
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Chọn filter status
+2. Nhập giá trị không hợp lệ
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Mở driver
+2. Chọn Edit
+3. Sửa thông tin
+4. Lưu</t>
+  </si>
+  <si>
+    <t>Driver: D01
+Thông tin hợp lệ</t>
+  </si>
+  <si>
+    <t>1. Nhập driver ID
+2. Cập nhật</t>
+  </si>
+  <si>
+    <t>1. Mở Edit
+2. Không nhập dữ liệu
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở thông tin driver
+2. Chọn Edit
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở trạng thái
+2. Chọn AVAILABLE
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở trạng thái
+2. Chọn BUSY
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Chọn status
+2. Nhập giá trị ngoài enum
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Không chọn status
+2. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở cập nhật vị trí
+2. Nhập latitude/longitude
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Nhập latitude biên
+2. Nhập longitude
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Nhập longitude biên
+2. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở cập nhật vị trí
+2. Bỏ một hoặc cả hai tọa độ
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Nhập tọa độ vượt giới hạn
+2. Lưu</t>
+  </si>
+  <si>
+    <t>1. Thực hiện cập nhật
+2. Mô phỏng lỗi service
+3. Kiểm tra kết quả</t>
+  </si>
+  <si>
+    <t>Role: CUSTOMER
+Driver: D01</t>
+  </si>
+  <si>
+    <t>Latitude: 10.7769
+Longitude: 106.7009</t>
+  </si>
+  <si>
+    <t>Latitude: null
+Longitude: null</t>
+  </si>
+  <si>
+    <t>Latitude: 91
+Longitude: 181</t>
+  </si>
+  <si>
+    <t>Driver: D01
+Service: unavailable</t>
+  </si>
+  <si>
+    <t>1. Driver mở trip
+2. Chọn Arrived
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Chuyển ARRIVED
+2. Chuyển PICKED_UP
+3. Chuyển IN_PROGRESS
+4. Chuyển COMPLETED</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Chọn IN_PROGRESS
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. D01 mở trip
+2. Cập nhật status</t>
+  </si>
+  <si>
+    <t>1. D02 mở T001
+2. Cập nhật status</t>
+  </si>
+  <si>
+    <t>1. Nhập trip ID
+2. Chọn status
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở Trip
+2. Nhập ID
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Nhập trip ID
+2. Xem</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Xem thông tin</t>
+  </si>
+  <si>
+    <t>1. Mở cập nhật status
+2. Không chọn status
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Nhập status ngoài danh sách
+2. Lưu</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập user khác
+2. Mở T001
+3. Cập nhật</t>
+  </si>
+  <si>
+    <t>1. Nhập ID không tồn tại
+2. Cập nhật</t>
+  </si>
+  <si>
+    <t>1. Mở Trip History
+2. Không nhập page/size</t>
+  </si>
+  <si>
+    <t>1. Mở history
+2. Nhập page=0,size=1
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Mở history
+2. Nhập size=100</t>
+  </si>
+  <si>
+    <t>1. Nhập size=0
+2. Thử lại size=101</t>
+  </si>
+  <si>
+    <t>1. Mở Trip History
+2. Không đăng nhập</t>
+  </si>
+  <si>
+    <t>1. Mở Rating
+2. Chọn 1 sao
+3. Gửi</t>
+  </si>
+  <si>
+    <t>1. Mở Rating
+2. Chọn 5 sao
+3. Gửi</t>
+  </si>
+  <si>
+    <t>1. Nhập score
+2. Gửi</t>
+  </si>
+  <si>
+    <t>1. Mở Rating
+2. Không chọn score
+3. Gửi</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Chọn Rating
+3. Gửi</t>
+  </si>
+  <si>
+    <t>1. C02 mở T001
+2. Chọn Rating
+3. Gửi</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Chọn Rating
+3. Gửi lần 2</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Cập nhật status
+3. Mô phỏng lỗi service</t>
+  </si>
+  <si>
+    <t>Driver: D01
+Trip: T001</t>
+  </si>
+  <si>
+    <t>Driver: D02
+Trip: T001</t>
+  </si>
+  <si>
+    <t>Trip: T001
+Score: 4</t>
+  </si>
+  <si>
+    <t>Owner: C01
+Current: C02
+Score: 5</t>
+  </si>
+  <si>
+    <t>Status: IN_PROGRESS
+Score: 5</t>
+  </si>
+  <si>
+    <t>Page: 0
+Size: 1</t>
+  </si>
+  <si>
+    <t>Page: 0
+Size: 20</t>
+  </si>
+  <si>
+    <t>Page: 0
+Size: 100</t>
+  </si>
+  <si>
+    <t>Score: 1
+Comment: Good</t>
+  </si>
+  <si>
+    <t>Score: 5
+Comment: Excellent</t>
+  </si>
+  <si>
+    <t>Score: empty
+Comment: Good</t>
+  </si>
+  <si>
+    <t>T001
+Service: unavailable</t>
+  </si>
+  <si>
+    <t>1. Mở Payment
+2. Chọn Cash
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Mở Payment
+2. Chọn Electronic
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Chọn phương thức
+2. Gửi thanh toán</t>
+  </si>
+  <si>
+    <t>1. Mở Payment
+2. Không chọn method
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Mở Payment
+2. Chọn CASH
+3. Thanh toán</t>
+  </si>
+  <si>
+    <t>1. Thực hiện payment
+2. Gửi thêm card number/CVV
+3. Kiểm tra response/database</t>
+  </si>
+  <si>
+    <t>1. Gửi webhook
+2. Kiểm tra payment</t>
+  </si>
+  <si>
+    <t>1. Gửi webhook
+2. Bỏ từng trường bắt buộc</t>
+  </si>
+  <si>
+    <t>1. Gửi webhook
+2. Nhập status ngoài enum</t>
+  </si>
+  <si>
+    <t>1. Mở payment
+2. Chọn Retry</t>
+  </si>
+  <si>
+    <t>1. Nhập payment ID
+2. Chọn Retry</t>
+  </si>
+  <si>
+    <t>1. Chọn Retry
+2. Bỏ payment ID</t>
+  </si>
+  <si>
+    <t>1. Nhập dữ liệu tại giới hạn
+2. Thực hiện payment</t>
+  </si>
+  <si>
+    <t>Trip: T001
+Method: CASH</t>
+  </si>
+  <si>
+    <t>Trip: T001
+Status: IN_PROGRESS
+Method: CASH</t>
+  </si>
+  <si>
+    <t>Card Number: test-card-number
+CVV: 123</t>
+  </si>
+  <si>
+    <t>Payment ID: P001
+Status: SUCCESS</t>
+  </si>
+  <si>
+    <t>Payment ID: P001
+Status: FAILED</t>
+  </si>
+  <si>
+    <t>PaymentId: empty
+Status: SUCCESS</t>
+  </si>
+  <si>
+    <t>Payment: P001
+Status: FAILED</t>
+  </si>
+  <si>
+    <t>Payment: P001
+Status: SUCCESS</t>
+  </si>
+  <si>
+    <t>1. Mở Notifications
+2. Xem danh sách</t>
+  </si>
+  <si>
+    <t>1. Mở Notifications
+2. Không đăng nhập</t>
+  </si>
+  <si>
+    <t>1. Mở notification
+2. Chọn Mark as Read</t>
+  </si>
+  <si>
+    <t>1. Nhập notification ID
+2. Mark as Read</t>
+  </si>
+  <si>
+    <t>1. Chọn Mark as Read
+2. Không nhập ID</t>
+  </si>
+  <si>
+    <t>1. Mở Notifications
+2. Mô phỏng lỗi service</t>
+  </si>
+  <si>
+    <t>1. Mở Vehicle Management
+2. Xem danh sách</t>
+  </si>
+  <si>
+    <t>1. Mở Add Vehicle
+2. Chọn driver
+3. Chọn vehicle type
+4. Nhập biển số
+5. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở Add Vehicle
+2. Lần lượt bỏ driver/type/plate
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở Add Vehicle
+2. Nhập biển số sai
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở Add Vehicle
+2. Nhập thông tin
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở vehicle
+2. Chọn Edit
+3. Sửa thông tin
+4. Lưu</t>
+  </si>
+  <si>
+    <t>1. Nhập vehicle ID
+2. Cập nhật</t>
+  </si>
+  <si>
+    <t>1. Gửi update
+2. Không truyền body</t>
+  </si>
+  <si>
+    <t>1. Nhập plate tại giới hạn cho phép
+2. Lưu
+3. Thử vượt giới hạn</t>
+  </si>
+  <si>
+    <t>1. Tạo/update vehicle
+2. Mô phỏng lỗi service</t>
+  </si>
+  <si>
+    <t>Driver: D01
+Vehicle: CAR_4_SEATS
+Plate: 51A-12345</t>
+  </si>
+  <si>
+    <t>DriverId/VehicleTypeId/Plate
+Number: empty</t>
+  </si>
+  <si>
+    <t>Vehicle: V001
+Plate: 51A-99999</t>
+  </si>
+  <si>
+    <t>Vehicle: V001
+Service: unavailable</t>
+  </si>
+  <si>
+    <t>Full Name: Nguyen Van B
+Email: valid@example.com</t>
+  </si>
+  <si>
+    <t>Page: 1
+PageSize: 20</t>
+  </si>
+  <si>
+    <t>Page: 1
+PageSize: 100</t>
+  </si>
+  <si>
+    <t>User: U01
+Service: unavailable</t>
+  </si>
+  <si>
+    <t>1. Mở Profile
+2. Chọn My Profile</t>
+  </si>
+  <si>
+    <t>1. Mở Profile
+2. Không đăng nhập</t>
+  </si>
+  <si>
+    <t>1. Mở Profile
+2. Chọn Edit
+3. Sửa thông tin
+4. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở Edit
+2. Nhập email sai hoặc body null
+3. Lưu</t>
+  </si>
+  <si>
+    <t>1. Mở Customer Management
+2. Xem danh sách</t>
+  </si>
+  <si>
+    <t>1. Mở danh sách Customer
+2. Nhập pageSize=100</t>
+  </si>
+  <si>
+    <t>1. Nhập pageSize=0
+2. Thử lại pageSize=101</t>
+  </si>
+  <si>
+    <t>1. Mở Customer Management
+2. Nhập keyword
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Nhập user ID
+2. Xem</t>
+  </si>
+  <si>
+    <t>1. Thực hiện truy vấn/update user
+2. Mô phỏng lỗi</t>
+  </si>
+  <si>
+    <t>1. Mở Reports
+2. Chọn Trips
+3. Nhập from/to
+4. Xem</t>
+  </si>
+  <si>
+    <t>1. Mở Trips Report
+2. Nhập cùng ngày
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Mở Report
+2. Bỏ from hoặc to
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Nhập khoảng thời gian
+2. Xem report</t>
+  </si>
+  <si>
+    <t>1. Mở Revenue Report
+2. Nhập from/to
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Mở Revenue Report
+2. Nhập cùng ngày
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Mở Revenue Report
+2. Bỏ from/to
+3. Xem</t>
+  </si>
+  <si>
+    <t>1. Mở Reports
+2. Chọn Trips/Revenue</t>
+  </si>
+  <si>
+    <t>1. Nhập khoảng thời gian hợp lệ
+2. Xem report
+3. Mô phỏng lỗi</t>
+  </si>
+  <si>
+    <t>From: 2026-01-01
+To: 2026-01-31</t>
+  </si>
+  <si>
+    <t>From: 2026-01-01
+To: 2026-01-01</t>
+  </si>
+  <si>
+    <t>From: empty
+To: 2026-01-31</t>
+  </si>
+  <si>
+    <t>From: 2026-02-01
+To: 2026-01-01</t>
+  </si>
+  <si>
+    <t>From: empty
+To: empty</t>
+  </si>
+  <si>
+    <t>From: 2026-01-01
+To: 2026-01-31
+Service: unavailable</t>
+  </si>
+  <si>
+    <t>1. Đăng nhập
+2. Mở Operations
+3. Chọn Active Trips</t>
+  </si>
+  <si>
+    <t>1. Mở Operations
+2. Chọn Active Trips</t>
+  </si>
+  <si>
+    <t>1. Mở Operations
+2. Chọn Abnormal Trips</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Chọn Resolve
+3. Nhập resolution
+4. Nhập note
+5. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Mở trip
+2. Chọn Resolve
+3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Nhập trip ID
+2. Resolve</t>
+  </si>
+  <si>
+    <t>1. Mở Resolve
+2. Bỏ resolution/note3. Xác nhận</t>
+  </si>
+  <si>
+    <t>1. Mở Transactions
+2. Chọn status SUCCESS</t>
+  </si>
+  <si>
+    <t>1. Mở Transactions
+2. Nhập from/to
+3. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Nhập from/to
+2. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Mở Transactions
+2. Không nhập filter</t>
+  </si>
+  <si>
+    <t>1. Nhập from và to cùng ngày
+2. Tìm kiếm</t>
+  </si>
+  <si>
+    <t>Trip: T001
+Resolution: REFUND
+Note: Customer refund</t>
+  </si>
+  <si>
+    <t>Resolution: empty
+Note: empty</t>
+  </si>
+  <si>
+    <t>Trip: T001
+Status: COMPLETED</t>
   </si>
 </sst>
 </file>
@@ -2588,9 +2927,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="12"/>
-      <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <scheme val="major"/>
@@ -2666,6 +3003,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2986,20 +3327,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B84287-A9CA-4B52-A1A1-6479B95272FB}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="17.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.09765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.69921875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.19921875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.796875" style="2"/>
+    <col min="1" max="4" width="17.8984375" style="2"/>
+    <col min="5" max="5" width="29.19921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.59765625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="17.8984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3025,7 +3361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" ht="156" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -3033,25 +3369,25 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>281</v>
+        <v>633</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>278</v>
+        <v>634</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -3059,25 +3395,25 @@
         <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>285</v>
+        <v>635</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -3085,25 +3421,25 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>289</v>
+        <v>636</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>290</v>
+        <v>641</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -3111,25 +3447,25 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>292</v>
+        <v>637</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>794</v>
+        <v>608</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="2" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -3137,71 +3473,71 @@
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>296</v>
+        <v>638</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>795</v>
+        <v>609</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="2" customFormat="1" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>299</v>
+        <v>639</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="2" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>303</v>
+        <v>640</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
@@ -3209,8 +3545,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="mailto:customer01@example.com" xr:uid="{10D65881-C5B7-4A7D-9263-3EA4C1F95B4C}"/>
-    <hyperlink ref="F4" r:id="rId2" display="mailto:customer01@example.com" xr:uid="{DF4B0FF3-80F9-4203-89E6-4316CAF1A9FD}"/>
+    <hyperlink ref="F4" r:id="rId1" display="mailto:customer01@example.com" xr:uid="{DF4B0FF3-80F9-4203-89E6-4316CAF1A9FD}"/>
+    <hyperlink ref="F2" r:id="rId2" display="mailto:customer01@example.com" xr:uid="{10D65881-C5B7-4A7D-9263-3EA4C1F95B4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -3224,10 +3560,10 @@
   <cols>
     <col min="1" max="1" width="17.3984375" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.19921875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.09765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.19921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.09765625" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.59765625" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
@@ -3258,27 +3594,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>675</v>
+        <v>533</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>676</v>
+        <v>826</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>677</v>
+        <v>534</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>678</v>
+        <v>535</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
@@ -3286,25 +3622,25 @@
     </row>
     <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>679</v>
+        <v>536</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>680</v>
+        <v>827</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
@@ -3312,25 +3648,25 @@
     </row>
     <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>682</v>
+        <v>538</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>683</v>
+        <v>539</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>684</v>
+        <v>540</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -3338,25 +3674,25 @@
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>684</v>
+        <v>540</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>685</v>
+        <v>541</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>686</v>
+        <v>542</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
@@ -3364,25 +3700,25 @@
     </row>
     <row r="6" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>687</v>
+        <v>543</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>675</v>
+        <v>533</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>688</v>
+        <v>828</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>677</v>
+        <v>534</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>689</v>
+        <v>544</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -3390,25 +3726,25 @@
     </row>
     <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>690</v>
+        <v>545</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>691</v>
+        <v>546</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
@@ -3416,51 +3752,51 @@
     </row>
     <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>691</v>
+        <v>546</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>692</v>
+        <v>547</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>686</v>
+        <v>542</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>693</v>
+        <v>829</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>694</v>
+        <v>838</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
@@ -3468,25 +3804,25 @@
     </row>
     <row r="10" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>696</v>
+        <v>549</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>697</v>
+        <v>830</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
@@ -3494,77 +3830,77 @@
     </row>
     <row r="11" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>698</v>
+        <v>831</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>516</v>
+        <v>424</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>699</v>
+        <v>550</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="B13" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>702</v>
+        <v>551</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>697</v>
+        <v>830</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>703</v>
+        <v>840</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>704</v>
+        <v>552</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
@@ -3572,51 +3908,51 @@
     </row>
     <row r="14" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>705</v>
+        <v>833</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>706</v>
+        <v>553</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>707</v>
+        <v>554</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>708</v>
+        <v>555</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>709</v>
+        <v>834</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>711</v>
+        <v>556</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
@@ -3624,25 +3960,25 @@
     </row>
     <row r="16" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>712</v>
+        <v>557</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>713</v>
+        <v>835</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>714</v>
+        <v>823</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>715</v>
+        <v>558</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
@@ -3650,25 +3986,25 @@
     </row>
     <row r="17" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>716</v>
+        <v>559</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>717</v>
+        <v>836</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>718</v>
+        <v>560</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
@@ -3676,51 +4012,51 @@
     </row>
     <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>719</v>
+        <v>561</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>721</v>
+        <v>563</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>722</v>
+        <v>837</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>723</v>
+        <v>821</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>724</v>
+        <v>564</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
@@ -3740,8 +4076,8 @@
     <col min="2" max="2" width="16.09765625" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.19921875" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.19921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.8984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.8984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.19921875" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.09765625" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.8984375" style="2" customWidth="1"/>
     <col min="9" max="16384" width="8.796875" style="2"/>
@@ -3773,209 +4109,209 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>725</v>
+        <v>565</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>726</v>
+        <v>566</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>727</v>
+        <v>811</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>728</v>
+        <v>567</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>729</v>
+        <v>568</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>730</v>
+        <v>812</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>723</v>
+        <v>821</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>731</v>
+        <v>569</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>732</v>
+        <v>570</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>733</v>
+        <v>813</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>734</v>
+        <v>822</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>735</v>
+        <v>571</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>736</v>
+        <v>572</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>737</v>
+        <v>814</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>714</v>
+        <v>823</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>449</v>
+        <v>384</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>738</v>
+        <v>573</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>726</v>
+        <v>566</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>739</v>
+        <v>815</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>740</v>
+        <v>574</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>741</v>
+        <v>816</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>723</v>
+        <v>821</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>742</v>
+        <v>575</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>743</v>
+        <v>576</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>744</v>
+        <v>817</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>745</v>
+        <v>824</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>746</v>
+        <v>577</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>747</v>
+        <v>818</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>748</v>
+        <v>578</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
@@ -3983,25 +4319,25 @@
     </row>
     <row r="10" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>749</v>
+        <v>579</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>750</v>
+        <v>580</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>751</v>
+        <v>819</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>752</v>
+        <v>825</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
@@ -4017,7 +4353,10 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="14.19921875" style="2"/>
+    <col min="1" max="4" width="14.19921875" style="2"/>
+    <col min="5" max="5" width="28.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.69921875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="14.19921875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -4048,103 +4387,103 @@
     </row>
     <row r="2" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>753</v>
+        <v>801</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>754</v>
+        <v>581</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>755</v>
+        <v>582</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>756</v>
+        <v>583</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>757</v>
+        <v>802</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>758</v>
+        <v>584</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>759</v>
+        <v>803</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>760</v>
+        <v>797</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>761</v>
+        <v>585</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>762</v>
+        <v>804</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>763</v>
+        <v>586</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>764</v>
+        <v>587</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
@@ -4152,129 +4491,129 @@
     </row>
     <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>765</v>
+        <v>588</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>767</v>
+        <v>798</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>768</v>
+        <v>589</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>769</v>
+        <v>590</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>770</v>
+        <v>806</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>771</v>
+        <v>799</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>772</v>
+        <v>591</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>773</v>
+        <v>592</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>774</v>
+        <v>807</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>775</v>
+        <v>593</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>776</v>
+        <v>594</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>777</v>
+        <v>808</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>778</v>
+        <v>595</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>686</v>
+        <v>542</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>651</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>779</v>
+        <v>596</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>780</v>
+        <v>597</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
@@ -4282,25 +4621,25 @@
     </row>
     <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>781</v>
+        <v>809</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>782</v>
+        <v>598</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>783</v>
+        <v>599</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
@@ -4308,25 +4647,25 @@
     </row>
     <row r="12" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>781</v>
+        <v>809</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>784</v>
+        <v>600</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -4334,60 +4673,57 @@
     </row>
     <row r="13" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>785</v>
+        <v>601</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>786</v>
+        <v>602</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>787</v>
+        <v>603</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>788</v>
+        <v>604</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>789</v>
+        <v>605</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>790</v>
+        <v>606</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>793</v>
+        <v>607</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" display="mailto:valid@example.com" xr:uid="{AB85A253-9761-4B11-AEB2-CEDAAC6E5DEA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4397,7 +4733,10 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="16.296875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="16.296875" style="2"/>
+    <col min="1" max="4" width="16.296875" style="2"/>
+    <col min="5" max="5" width="30.3984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.3984375" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="16.296875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4426,27 +4765,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>796</v>
+        <v>610</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>798</v>
+        <v>611</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>799</v>
+        <v>612</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
@@ -4454,25 +4793,25 @@
     </row>
     <row r="3" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>800</v>
+        <v>613</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>801</v>
+        <v>614</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>681</v>
+        <v>537</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
@@ -4480,77 +4819,77 @@
     </row>
     <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>802</v>
+        <v>615</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>803</v>
+        <v>616</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>801</v>
+        <v>614</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>804</v>
+        <v>617</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>686</v>
+        <v>542</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="93.6" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>805</v>
+        <v>618</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>806</v>
+        <v>619</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>809</v>
+        <v>620</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -4558,25 +4897,25 @@
     </row>
     <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>812</v>
+        <v>621</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>813</v>
+        <v>786</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>814</v>
+        <v>622</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>815</v>
+        <v>623</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
@@ -4584,51 +4923,51 @@
     </row>
     <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>816</v>
+        <v>787</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>460</v>
+        <v>713</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>817</v>
+        <v>788</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>818</v>
+        <v>795</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>819</v>
+        <v>624</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
@@ -4636,77 +4975,77 @@
     </row>
     <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>820</v>
+        <v>789</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>821</v>
+        <v>625</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>822</v>
+        <v>626</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>824</v>
+        <v>627</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>825</v>
+        <v>791</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>826</v>
+        <v>628</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>827</v>
+        <v>629</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
@@ -4714,25 +5053,25 @@
     </row>
     <row r="13" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>828</v>
+        <v>630</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>829</v>
+        <v>631</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>830</v>
+        <v>792</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>831</v>
+        <v>796</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>832</v>
+        <v>632</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
@@ -4751,9 +5090,10 @@
     <col min="1" max="1" width="15.3984375" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.296875" style="2" customWidth="1"/>
     <col min="3" max="3" width="14.19921875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" style="2" customWidth="1"/>
     <col min="5" max="5" width="28.8984375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="18.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.19921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
@@ -4794,42 +5134,42 @@
         <v>25</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>642</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>652</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
@@ -4837,25 +5177,25 @@
     </row>
     <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>311</v>
+        <v>643</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>653</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -4863,25 +5203,25 @@
     </row>
     <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>315</v>
+        <v>644</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>316</v>
+        <v>654</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
@@ -4889,25 +5229,25 @@
     </row>
     <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>319</v>
+        <v>645</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>320</v>
+        <v>655</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -4915,25 +5255,25 @@
     </row>
     <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>323</v>
+        <v>646</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>324</v>
+        <v>656</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
@@ -4941,25 +5281,25 @@
     </row>
     <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>327</v>
+        <v>647</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>657</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
@@ -4967,25 +5307,25 @@
     </row>
     <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>330</v>
+        <v>648</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>39</v>
+        <v>658</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
@@ -4993,51 +5333,51 @@
     </row>
     <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>332</v>
+        <v>649</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>336</v>
+        <v>650</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>43</v>
+        <v>659</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
@@ -5058,8 +5398,8 @@
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.09765625" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.19921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.69921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.8984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.19921875" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.59765625" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
@@ -5092,25 +5432,25 @@
     </row>
     <row r="2" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>340</v>
+        <v>660</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
@@ -5118,25 +5458,25 @@
     </row>
     <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>345</v>
+        <v>661</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
@@ -5144,25 +5484,25 @@
     </row>
     <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>349</v>
+        <v>662</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -5170,25 +5510,25 @@
     </row>
     <row r="5" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>352</v>
+        <v>663</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
@@ -5196,25 +5536,25 @@
     </row>
     <row r="6" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>356</v>
+        <v>664</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -5233,10 +5573,10 @@
     <col min="1" max="1" width="17.796875" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.19921875" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.296875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.69921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.8984375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.59765625" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.296875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.796875" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
@@ -5268,103 +5608,103 @@
     </row>
     <row r="2" spans="1:8" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>361</v>
+        <v>665</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>362</v>
+        <v>685</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>366</v>
+        <v>666</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>369</v>
+        <v>667</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>370</v>
+        <v>686</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>372</v>
+        <v>668</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>373</v>
+        <v>687</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
@@ -5372,25 +5712,25 @@
     </row>
     <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>375</v>
+        <v>669</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -5398,25 +5738,25 @@
     </row>
     <row r="7" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>377</v>
+        <v>670</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>378</v>
+        <v>337</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>379</v>
+        <v>338</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
@@ -5424,51 +5764,51 @@
     </row>
     <row r="8" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>381</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>384</v>
+        <v>672</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
@@ -5476,25 +5816,25 @@
     </row>
     <row r="10" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>388</v>
+        <v>673</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
@@ -5502,25 +5842,25 @@
     </row>
     <row r="11" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>390</v>
+        <v>674</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
@@ -5528,25 +5868,25 @@
     </row>
     <row r="12" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>393</v>
+        <v>675</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>395</v>
+        <v>349</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -5554,77 +5894,77 @@
     </row>
     <row r="13" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>396</v>
+        <v>350</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>397</v>
+        <v>676</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>401</v>
+        <v>677</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>402</v>
+        <v>354</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>403</v>
+        <v>355</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>404</v>
+        <v>356</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>405</v>
+        <v>678</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>406</v>
+        <v>688</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>407</v>
+        <v>357</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
@@ -5632,25 +5972,25 @@
     </row>
     <row r="16" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>408</v>
+        <v>679</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
@@ -5658,25 +5998,25 @@
     </row>
     <row r="17" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>410</v>
+        <v>359</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>411</v>
+        <v>680</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>412</v>
+        <v>689</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>413</v>
+        <v>360</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
@@ -5684,129 +6024,129 @@
     </row>
     <row r="18" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>414</v>
+        <v>361</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>415</v>
+        <v>681</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>416</v>
+        <v>690</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>417</v>
+        <v>362</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>418</v>
+        <v>363</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>419</v>
+        <v>691</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>420</v>
+        <v>364</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>421</v>
+        <v>682</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>412</v>
+        <v>689</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>422</v>
+        <v>365</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>424</v>
+        <v>683</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>425</v>
+        <v>692</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>427</v>
+        <v>368</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>428</v>
+        <v>369</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>429</v>
+        <v>370</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>430</v>
+        <v>684</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>431</v>
+        <v>693</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>432</v>
+        <v>371</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>22</v>
@@ -5822,7 +6162,9 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="21.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="21.19921875" style="2"/>
+    <col min="1" max="4" width="21.19921875" style="2"/>
+    <col min="5" max="5" width="28.796875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="21.19921875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -5853,77 +6195,77 @@
     </row>
     <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>433</v>
+        <v>372</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>434</v>
+        <v>373</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>435</v>
+        <v>694</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>436</v>
+        <v>374</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>438</v>
+        <v>376</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>439</v>
+        <v>695</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>441</v>
+        <v>378</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>442</v>
+        <v>379</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>443</v>
+        <v>696</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>444</v>
+        <v>380</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>445</v>
+        <v>381</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -5931,51 +6273,51 @@
     </row>
     <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>446</v>
+        <v>382</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>447</v>
+        <v>697</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>448</v>
+        <v>383</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>449</v>
+        <v>384</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>450</v>
+        <v>698</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>451</v>
+        <v>699</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -5983,51 +6325,51 @@
     </row>
     <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>452</v>
+        <v>700</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>453</v>
+        <v>385</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>455</v>
+        <v>387</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>456</v>
+        <v>701</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>457</v>
+        <v>388</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
@@ -6035,103 +6377,103 @@
     </row>
     <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>458</v>
+        <v>389</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>459</v>
+        <v>702</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>460</v>
+        <v>713</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>461</v>
+        <v>390</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>462</v>
+        <v>391</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>463</v>
+        <v>703</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>465</v>
+        <v>393</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>466</v>
+        <v>704</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>467</v>
+        <v>394</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>468</v>
+        <v>395</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>469</v>
+        <v>705</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>448</v>
+        <v>383</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>470</v>
+        <v>396</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -6139,25 +6481,25 @@
     </row>
     <row r="13" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>472</v>
+        <v>706</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
@@ -6165,51 +6507,51 @@
     </row>
     <row r="14" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>475</v>
+        <v>707</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>476</v>
+        <v>714</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>477</v>
+        <v>400</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>478</v>
+        <v>708</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>479</v>
+        <v>401</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>480</v>
+        <v>402</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
@@ -6217,25 +6559,25 @@
     </row>
     <row r="16" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>481</v>
+        <v>403</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>483</v>
+        <v>404</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>480</v>
+        <v>402</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
@@ -6243,25 +6585,25 @@
     </row>
     <row r="17" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>484</v>
+        <v>405</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>485</v>
+        <v>710</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>486</v>
+        <v>715</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>487</v>
+        <v>406</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
@@ -6269,25 +6611,25 @@
     </row>
     <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>489</v>
+        <v>711</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>490</v>
+        <v>716</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
@@ -6295,25 +6637,25 @@
     </row>
     <row r="19" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>491</v>
+        <v>408</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>492</v>
+        <v>409</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>493</v>
+        <v>712</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>494</v>
+        <v>717</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
@@ -6333,8 +6675,8 @@
     <col min="2" max="2" width="17.296875" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.8984375" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.69921875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.296875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.59765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.69921875" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
@@ -6365,131 +6707,131 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>498</v>
+        <v>718</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>499</v>
+        <v>413</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>502</v>
+        <v>416</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>503</v>
+        <v>719</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>504</v>
+        <v>417</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>505</v>
+        <v>418</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>506</v>
+        <v>419</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>507</v>
+        <v>720</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>508</v>
+        <v>420</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>509</v>
+        <v>421</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>510</v>
+        <v>721</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>511</v>
+        <v>744</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>512</v>
+        <v>422</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>513</v>
+        <v>722</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>514</v>
+        <v>745</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -6497,25 +6839,25 @@
     </row>
     <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>515</v>
+        <v>723</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>516</v>
+        <v>424</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
@@ -6523,25 +6865,25 @@
     </row>
     <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>517</v>
+        <v>724</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>518</v>
+        <v>425</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>519</v>
+        <v>426</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
@@ -6549,25 +6891,25 @@
     </row>
     <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>520</v>
+        <v>725</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>516</v>
+        <v>424</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
@@ -6575,51 +6917,51 @@
     </row>
     <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>521</v>
+        <v>427</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>522</v>
+        <v>726</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>523</v>
+        <v>428</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>524</v>
+        <v>429</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>525</v>
+        <v>430</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>526</v>
+        <v>727</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
@@ -6627,129 +6969,129 @@
     </row>
     <row r="12" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>527</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>528</v>
+        <v>728</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>529</v>
+        <v>432</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>530</v>
+        <v>433</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>512</v>
+        <v>422</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>531</v>
+        <v>729</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>514</v>
+        <v>423</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>532</v>
+        <v>434</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>533</v>
+        <v>730</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>534</v>
+        <v>435</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>535</v>
+        <v>731</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>536</v>
+        <v>436</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>537</v>
+        <v>437</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>538</v>
+        <v>438</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>539</v>
+        <v>732</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>540</v>
+        <v>439</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>541</v>
+        <v>440</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
@@ -6757,77 +7099,77 @@
     </row>
     <row r="17" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>542</v>
+        <v>441</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>543</v>
+        <v>733</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>544</v>
+        <v>442</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>545</v>
+        <v>443</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>546</v>
+        <v>444</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>547</v>
+        <v>734</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>548</v>
+        <v>445</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>549</v>
+        <v>446</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>550</v>
+        <v>735</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
@@ -6835,25 +7177,25 @@
     </row>
     <row r="20" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>551</v>
+        <v>447</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>552</v>
+        <v>448</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>553</v>
+        <v>736</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>554</v>
+        <v>449</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>555</v>
+        <v>450</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
@@ -6861,25 +7203,25 @@
     </row>
     <row r="21" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>556</v>
+        <v>451</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>552</v>
+        <v>448</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>557</v>
+        <v>737</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>558</v>
+        <v>452</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>555</v>
+        <v>450</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
@@ -6887,25 +7229,25 @@
     </row>
     <row r="22" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>559</v>
+        <v>453</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>560</v>
+        <v>738</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>561</v>
+        <v>454</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>562</v>
+        <v>455</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>22</v>
@@ -6913,25 +7255,25 @@
     </row>
     <row r="23" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>563</v>
+        <v>456</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>564</v>
+        <v>739</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>565</v>
+        <v>457</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>566</v>
+        <v>458</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>22</v>
@@ -6939,25 +7281,25 @@
     </row>
     <row r="24" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>568</v>
+        <v>748</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>569</v>
+        <v>459</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>22</v>
@@ -6965,25 +7307,25 @@
     </row>
     <row r="25" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>571</v>
+        <v>461</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>572</v>
+        <v>741</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>573</v>
+        <v>747</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>574</v>
+        <v>462</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>22</v>
@@ -6991,51 +7333,51 @@
     </row>
     <row r="26" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>575</v>
+        <v>463</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>576</v>
+        <v>742</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>577</v>
+        <v>746</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>578</v>
+        <v>464</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>579</v>
+        <v>465</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>580</v>
+        <v>466</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>581</v>
+        <v>743</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>582</v>
+        <v>467</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>583</v>
+        <v>468</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>22</v>
@@ -7055,8 +7397,8 @@
     <col min="2" max="2" width="14.3984375" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.09765625" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
@@ -7087,79 +7429,79 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>498</v>
+        <v>718</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>499</v>
+        <v>413</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="124.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>502</v>
+        <v>416</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>503</v>
+        <v>719</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>504</v>
+        <v>417</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>505</v>
+        <v>418</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>506</v>
+        <v>419</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>507</v>
+        <v>720</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>508</v>
+        <v>420</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -7167,51 +7509,51 @@
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>509</v>
+        <v>421</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>510</v>
+        <v>721</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>511</v>
+        <v>744</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>512</v>
+        <v>422</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>513</v>
+        <v>722</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>514</v>
+        <v>745</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
@@ -7219,51 +7561,51 @@
     </row>
     <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>515</v>
+        <v>723</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>516</v>
+        <v>424</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>517</v>
+        <v>724</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>518</v>
+        <v>425</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>519</v>
+        <v>426</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
@@ -7271,25 +7613,25 @@
     </row>
     <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>520</v>
+        <v>725</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>516</v>
+        <v>424</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
@@ -7297,51 +7639,51 @@
     </row>
     <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>521</v>
+        <v>427</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>522</v>
+        <v>726</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>523</v>
+        <v>428</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>524</v>
+        <v>429</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>525</v>
+        <v>430</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>526</v>
+        <v>727</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
@@ -7349,25 +7691,25 @@
     </row>
     <row r="12" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>527</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>528</v>
+        <v>728</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>529</v>
+        <v>432</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -7375,51 +7717,51 @@
     </row>
     <row r="13" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>530</v>
+        <v>433</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>512</v>
+        <v>422</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>531</v>
+        <v>729</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>514</v>
+        <v>745</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>532</v>
+        <v>434</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>533</v>
+        <v>730</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
@@ -7427,51 +7769,51 @@
     </row>
     <row r="15" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>534</v>
+        <v>435</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>535</v>
+        <v>731</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>536</v>
+        <v>750</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>537</v>
+        <v>437</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>538</v>
+        <v>438</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>539</v>
+        <v>732</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>540</v>
+        <v>749</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>541</v>
+        <v>440</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
@@ -7479,25 +7821,25 @@
     </row>
     <row r="17" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>542</v>
+        <v>441</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>543</v>
+        <v>733</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>544</v>
+        <v>751</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>545</v>
+        <v>443</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
@@ -7505,51 +7847,51 @@
     </row>
     <row r="18" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>546</v>
+        <v>444</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>547</v>
+        <v>734</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>548</v>
+        <v>445</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>549</v>
+        <v>446</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>550</v>
+        <v>735</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
@@ -7557,25 +7899,25 @@
     </row>
     <row r="20" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>551</v>
+        <v>447</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>552</v>
+        <v>448</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>553</v>
+        <v>736</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>554</v>
+        <v>752</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>555</v>
+        <v>450</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
@@ -7583,25 +7925,25 @@
     </row>
     <row r="21" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>556</v>
+        <v>451</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>552</v>
+        <v>448</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>557</v>
+        <v>737</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>558</v>
+        <v>753</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>555</v>
+        <v>450</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
@@ -7609,25 +7951,25 @@
     </row>
     <row r="22" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>559</v>
+        <v>453</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>560</v>
+        <v>738</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>561</v>
+        <v>454</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>562</v>
+        <v>455</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>22</v>
@@ -7635,25 +7977,25 @@
     </row>
     <row r="23" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>563</v>
+        <v>456</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>564</v>
+        <v>739</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>565</v>
+        <v>754</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>566</v>
+        <v>458</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>22</v>
@@ -7661,25 +8003,25 @@
     </row>
     <row r="24" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>567</v>
+        <v>740</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>568</v>
+        <v>748</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>569</v>
+        <v>459</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>22</v>
@@ -7687,25 +8029,25 @@
     </row>
     <row r="25" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>570</v>
+        <v>460</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>571</v>
+        <v>461</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>572</v>
+        <v>741</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>573</v>
+        <v>747</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>574</v>
+        <v>462</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>22</v>
@@ -7713,25 +8055,25 @@
     </row>
     <row r="26" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>575</v>
+        <v>463</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>576</v>
+        <v>742</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>577</v>
+        <v>746</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>578</v>
+        <v>464</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>22</v>
@@ -7739,25 +8081,25 @@
     </row>
     <row r="27" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>579</v>
+        <v>465</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>580</v>
+        <v>466</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>581</v>
+        <v>743</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>582</v>
+        <v>755</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>583</v>
+        <v>468</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>22</v>
@@ -7777,8 +8119,8 @@
     <col min="2" max="2" width="18.796875" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.69921875" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.09765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.19921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.3984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="26.796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.796875" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
@@ -7809,27 +8151,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>584</v>
+        <v>756</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>585</v>
+        <v>769</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>586</v>
+        <v>469</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
@@ -7837,259 +8179,259 @@
     </row>
     <row r="3" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>587</v>
+        <v>470</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>588</v>
+        <v>757</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>589</v>
+        <v>471</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>590</v>
+        <v>472</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>592</v>
+        <v>758</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>593</v>
+        <v>474</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>594</v>
+        <v>475</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>595</v>
+        <v>759</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>596</v>
+        <v>476</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>597</v>
+        <v>477</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>598</v>
+        <v>760</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>599</v>
+        <v>770</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="78" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>600</v>
+        <v>478</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>601</v>
+        <v>479</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>602</v>
+        <v>761</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>603</v>
+        <v>771</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>604</v>
+        <v>480</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>605</v>
+        <v>481</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>606</v>
+        <v>762</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>607</v>
+        <v>772</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>608</v>
+        <v>482</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>606</v>
+        <v>762</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>609</v>
+        <v>773</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>610</v>
+        <v>483</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>611</v>
+        <v>484</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>612</v>
+        <v>485</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>613</v>
+        <v>763</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>614</v>
+        <v>774</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>615</v>
+        <v>486</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>616</v>
+        <v>487</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>612</v>
+        <v>485</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>617</v>
+        <v>764</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>618</v>
+        <v>488</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>619</v>
+        <v>489</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>620</v>
+        <v>490</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>621</v>
+        <v>765</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>622</v>
+        <v>775</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>623</v>
+        <v>491</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
@@ -8097,25 +8439,25 @@
     </row>
     <row r="13" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>624</v>
+        <v>492</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>621</v>
+        <v>765</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>625</v>
+        <v>776</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
@@ -8123,25 +8465,25 @@
     </row>
     <row r="14" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>626</v>
+        <v>766</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>627</v>
+        <v>493</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>628</v>
+        <v>494</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
@@ -8149,25 +8491,25 @@
     </row>
     <row r="15" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>629</v>
+        <v>495</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>630</v>
+        <v>767</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>631</v>
+        <v>496</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
@@ -8175,25 +8517,25 @@
     </row>
     <row r="16" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>632</v>
+        <v>497</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>633</v>
+        <v>498</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>634</v>
+        <v>499</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>635</v>
+        <v>768</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>636</v>
+        <v>500</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>637</v>
+        <v>501</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
@@ -8209,11 +8551,12 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.59765625" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.3984375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.19921875" style="2" customWidth="1"/>
-    <col min="5" max="6" width="13.59765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.19921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="2"/>
   </cols>
@@ -8244,27 +8587,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>638</v>
+        <v>502</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>640</v>
+        <v>504</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>641</v>
+        <v>505</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>642</v>
+        <v>777</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>643</v>
+        <v>506</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>644</v>
+        <v>507</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
@@ -8272,51 +8615,51 @@
     </row>
     <row r="3" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>645</v>
+        <v>508</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>646</v>
+        <v>509</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>647</v>
+        <v>510</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>648</v>
+        <v>511</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>649</v>
+        <v>512</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>650</v>
+        <v>513</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>651</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>652</v>
+        <v>515</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>653</v>
+        <v>516</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>654</v>
+        <v>778</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -8324,25 +8667,25 @@
     </row>
     <row r="5" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>655</v>
+        <v>517</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>656</v>
+        <v>518</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>657</v>
+        <v>519</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>658</v>
+        <v>779</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>659</v>
+        <v>520</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>660</v>
+        <v>521</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
@@ -8350,51 +8693,51 @@
     </row>
     <row r="6" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>661</v>
+        <v>522</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>662</v>
+        <v>523</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>663</v>
+        <v>780</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>664</v>
+        <v>524</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>665</v>
+        <v>525</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>666</v>
+        <v>526</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>667</v>
+        <v>781</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>668</v>
+        <v>527</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>669</v>
+        <v>528</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
@@ -8402,25 +8745,25 @@
     </row>
     <row r="8" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>670</v>
+        <v>529</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>639</v>
+        <v>503</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>671</v>
+        <v>530</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>672</v>
+        <v>531</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>673</v>
+        <v>782</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>674</v>
+        <v>532</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
